--- a/addons/stock/static/xlsx/stock_quant.xlsx
+++ b/addons/stock/static/xlsx/stock_quant.xlsx
@@ -1,94 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Product</t>
   </si>
   <si>
-    <t>Lot/Serial Number</t>
+    <t xml:space="preserve">Lot/Serial Number</t>
   </si>
   <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Counted Quantity</t>
-  </si>
-  <si>
-    <t>Difference</t>
-  </si>
-  <si>
-    <t>Scheduled Date</t>
-  </si>
-  <si>
-    <t>Assigned To</t>
-  </si>
-  <si>
-    <t>[FURN_0789] Individual Workplace</t>
-  </si>
-  <si>
-    <t>[E-COM08] Storage Box</t>
-  </si>
-  <si>
-    <t>[E-COM07] Large Cabinet</t>
-  </si>
-  <si>
-    <t>[E-COM10] Pedal Bin</t>
-  </si>
-  <si>
-    <t>[E-COM11] Cabinet with Doors</t>
-  </si>
-  <si>
-    <t>[E-COM12] Conference Chair (Steel)</t>
-  </si>
-  <si>
-    <t>[E-COM13] Conference Chair (Aluminium)</t>
-  </si>
-  <si>
-    <t>[FURN_0096] Customizable Desk (Steel, White)</t>
-  </si>
-  <si>
-    <t>[FURN_0097] Customizable Desk (Steel, Black)</t>
-  </si>
-  <si>
-    <t>[FURN_0098] Customizable Desk (Aluminium, White)</t>
-  </si>
-  <si>
-    <t>[DESK0004] Customizable Desk (Aluminium, Black)</t>
-  </si>
-  <si>
-    <t>[FURN_0269] Office Chair Black</t>
-  </si>
-  <si>
-    <t>[FURN_1118] Corner Desk Left Sit</t>
-  </si>
-  <si>
-    <t>[FURN_8855] Drawer</t>
+    <t xml:space="preserve">Counted Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assigned To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_0789] Individual Workplace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[E-COM08] Storage Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[E-COM07] Large Cabinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[E-COM10] Pedal Bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[E-COM11] Cabinet with Doors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[E-COM12] Conference Chair (Steel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[E-COM13] Conference Chair (Aluminium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_0096] Customizable Desk (Steel, White)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_0097] Customizable Desk (Steel, Black)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_0098] Customizable Desk (Aluminium, White)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[DESK0004] Customizable Desk (Aluminium, Black)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_0269] Office Chair Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_1118] Corner Desk Left Sit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_8855] Drawer</t>
   </si>
   <si>
     <t>0000000000029</t>
   </si>
   <si>
-    <t>[FURN_7800] Desk Combination</t>
-  </si>
-  <si>
-    <t>[FURN_6666] Acoustic Bloc Screens</t>
-  </si>
-  <si>
-    <t>[FURN_5555] Cable Management Box</t>
+    <t xml:space="preserve">[FURN_7800] Desk Combination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_6666] Acoustic Bloc Screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[FURN_5555] Cable Management Box</t>
   </si>
   <si>
     <t>CM-BOX-00001</t>
@@ -100,24 +99,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -131,23 +128,23 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -155,11 +152,16 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -205,13 +207,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -239,13 +241,13 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -442,15 +444,234 @@
 </a:theme>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="30.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="7" width="30.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,13 +690,10 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2">
@@ -484,17 +702,14 @@
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="E2" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2">
@@ -503,17 +718,14 @@
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="E3" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2">
@@ -522,17 +734,14 @@
       <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="E4" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2">
@@ -541,17 +750,14 @@
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="E5" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -560,17 +766,14 @@
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="E6" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
@@ -579,17 +782,14 @@
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="E7" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" ht="28.5">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -598,17 +798,14 @@
       <c r="D8" s="2">
         <v>0</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="E8" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" ht="28.5">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -617,17 +814,14 @@
       <c r="D9" s="2">
         <v>0</v>
       </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="E9" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="28.5">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -636,17 +830,14 @@
       <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="E10" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="28.5">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -655,17 +846,14 @@
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="E11" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="28.5">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -674,17 +862,14 @@
       <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="E12" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13">
       <c r="A13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -693,17 +878,14 @@
       <c r="D13" s="2">
         <v>0</v>
       </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="E13" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
@@ -712,20 +894,17 @@
       <c r="D14" s="2">
         <v>0</v>
       </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="E14" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15">
       <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C15" s="2">
         <v>80</v>
@@ -733,17 +912,14 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="E15" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
@@ -752,17 +928,14 @@
       <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="E16" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2">
@@ -771,20 +944,17 @@
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="E17" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" ht="28.5">
       <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C18" s="2">
         <v>50</v>
@@ -792,20 +962,17 @@
       <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="E18" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" ht="28.5">
       <c r="A19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2">
         <v>40</v>
@@ -813,15 +980,15 @@
       <c r="D19" s="2">
         <v>0</v>
       </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44926</v>
-      </c>
-      <c r="G19" s="2"/>
+      <c r="E19" s="3">
+        <v>44926</v>
+      </c>
+      <c r="F19" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>